--- a/test/fixtures/xlsx/core/core.xlsx
+++ b/test/fixtures/xlsx/core/core.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="242">
   <si>
     <t xml:space="preserve">:enum ValueType</t>
   </si>
@@ -711,6 +711,39 @@
   </si>
   <si>
     <t xml:space="preserve">identifies this data build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze;silver;gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thresholds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10;50;100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one element, where a separator has nowhere to go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common;Rare;Epic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enum elements</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2161,6 +2194,62 @@
         <v>230</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" t="s">
+        <v>232</v>
+      </c>
+      <c r="F12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" t="s">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
